--- a/DataRepo/data/tests/same_name_mzxmls/mzxml_study_doc_same_seq.xlsx
+++ b/DataRepo/data/tests/same_name_mzxmls/mzxml_study_doc_same_seq.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/data/tests/same_name_mzxmls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-LOCAL/TRACEBASE/tracebase/DataRepo/data/tests/same_name_mzxmls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E8387B-B30E-2A47-B29E-A5F840EA7B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4700821-F158-AC4B-A06C-52322B649C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="7040" windowWidth="29900" windowHeight="12800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9100" yWindow="2000" windowWidth="29900" windowHeight="12800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sequences" sheetId="9" r:id="rId1"/>
@@ -496,7 +496,7 @@
   <cols>
     <col min="1" max="1" width="13.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="37" style="2" customWidth="1"/>
     <col min="6" max="16384" width="10.83203125" style="2"/>
